--- a/manuscript/tables/e-table-3-medications.xlsx
+++ b/manuscript/tables/e-table-3-medications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/newer-glp1-dementia-repkit/manuscript/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C918C1A-EBCD-1C4F-93ED-4F7C9C82CE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F050A6B-F143-0846-8E94-3B2A5745ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Medications Considered" sheetId="3" r:id="rId1"/>
@@ -68,212 +68,212 @@
     <t>Generic Name</t>
   </si>
   <si>
-    <t>SEGLUROMET</t>
-  </si>
-  <si>
-    <t>EMPAGLIFLOZIN</t>
-  </si>
-  <si>
-    <t>SYNJARDY</t>
-  </si>
-  <si>
-    <t>CANAGLIFLOZIN</t>
-  </si>
-  <si>
-    <t>INVOKANA</t>
-  </si>
-  <si>
-    <t>INVOKAMET</t>
-  </si>
-  <si>
-    <t>DAPAGLIFLOZIN, FARXIGA</t>
-  </si>
-  <si>
-    <t>STEGLATRO</t>
-  </si>
-  <si>
-    <t>BEXAGLIFLOZIN</t>
-  </si>
-  <si>
-    <t>SOTAGLIFLOZIN</t>
-  </si>
-  <si>
-    <t>INPEFA</t>
-  </si>
-  <si>
     <t>Drug Names</t>
   </si>
   <si>
-    <t>DAPAGLIFLOZIN PROPANEDIOL</t>
-  </si>
-  <si>
-    <t>DAPAGLIFLOZIN PROPANEDIOL/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>CANAGLIFLOZIN/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>JARDIANCE</t>
-  </si>
-  <si>
-    <t>ERTUGLIFLOZIN PIDOLATE/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>ERTUGLIFLOZIN PIDOLATE</t>
-  </si>
-  <si>
-    <t>EMPAGLIFLOZIN/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>BEXAGLIFLOZIN, BRENZAVVY</t>
-  </si>
-  <si>
-    <t>ALOGLIPTIN BENZOATE</t>
-  </si>
-  <si>
-    <t>ALOGLIPTIN BENZOATE/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>ALOGLIPTIN BENZOATE/PIOGLITAZONE HCL</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN HCL</t>
-  </si>
-  <si>
-    <t>BRYNOVIN</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN PHOSPHATE/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>JANUMET</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN PHOSPHATE</t>
-  </si>
-  <si>
-    <t>JANUVIA</t>
-  </si>
-  <si>
-    <t>LINAGLIPTIN/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN PHOSPHATE/SIMVASTATIN</t>
-  </si>
-  <si>
-    <t>JUVISYNC</t>
-  </si>
-  <si>
-    <t>SAXAGLIPTIN HCL/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>LINAGLIPTIN</t>
-  </si>
-  <si>
-    <t>SAXAGLIPTIN HCL</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>ZITUVIMET</t>
-  </si>
-  <si>
-    <t>DAPAGLIFLOZIN-METFORMIN, XIGDUO</t>
-  </si>
-  <si>
-    <t>ALOGLIPTIN, NESINA</t>
-  </si>
-  <si>
-    <t>ALOGLIPTIN-METFORMIN, KAZANO</t>
-  </si>
-  <si>
-    <t>ALOGLIPTIN-PIOGLITAZONE, OSENI</t>
-  </si>
-  <si>
-    <t>LINAGLIPTIN, TRADJENTA</t>
-  </si>
-  <si>
-    <t>JENTADUETO, LINAGLIPTIN-METFORMIN</t>
-  </si>
-  <si>
-    <t>ONGLYZA, KOMBIGLYZE</t>
-  </si>
-  <si>
-    <t>SAXAGLIPTIN-METFORMIN</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN, ZITUVIO</t>
-  </si>
-  <si>
-    <t>SITAGLIPTIN-METFORMIN, ZITUVIMET</t>
-  </si>
-  <si>
     <t>Sulfonylureas</t>
   </si>
   <si>
-    <t>GLIMEPIRIDE</t>
-  </si>
-  <si>
-    <t>GLIPIZIDE</t>
-  </si>
-  <si>
-    <t>GLIPIZIDE/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>GLYBURIDE</t>
-  </si>
-  <si>
-    <t>GLYBURIDE,MICRONIZED</t>
-  </si>
-  <si>
-    <t>GLYBURIDE/METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>PIOGLITAZONE HCL/GLIMEPIRIDE</t>
-  </si>
-  <si>
-    <t>PIOGLITAZONE-GLIMEPIRIDE</t>
-  </si>
-  <si>
-    <t>ROSIGLITAZONE MALEATE/GLIMEPIRIDE</t>
-  </si>
-  <si>
-    <t>AVANDARYL</t>
-  </si>
-  <si>
-    <t>GLIMEPIRIDE, AMARYL</t>
-  </si>
-  <si>
-    <t>GLIPIZIDE, GLUCOTROL</t>
-  </si>
-  <si>
-    <t>GLIPIZIDE-METFORMIN, METAGLIP</t>
-  </si>
-  <si>
-    <t>DIABETA, GLYBURIDE, MICRONASE</t>
-  </si>
-  <si>
-    <t>GLYBURIDE MICRONIZED, GLYCRON, GLYNASE</t>
-  </si>
-  <si>
-    <t>GLUCOVANCE, GLYBURIDE-METFORMIN HCL</t>
-  </si>
-  <si>
-    <t>DUETACT, PIOGLITAZONE-GLIMEPIRIDE</t>
-  </si>
-  <si>
     <t>Comparators</t>
+  </si>
+  <si>
+    <t>Alogliptin Benzoate</t>
+  </si>
+  <si>
+    <t>Alogliptin, Nesina</t>
+  </si>
+  <si>
+    <t>Alogliptin Benzoate/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Alogliptin-Metformin, Kazano</t>
+  </si>
+  <si>
+    <t>Alogliptin Benzoate/Pioglitazone Hcl</t>
+  </si>
+  <si>
+    <t>Alogliptin-Pioglitazone, Oseni</t>
+  </si>
+  <si>
+    <t>Linagliptin</t>
+  </si>
+  <si>
+    <t>Linagliptin, Tradjenta</t>
+  </si>
+  <si>
+    <t>Linagliptin/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Jentadueto, Linagliptin-Metformin</t>
+  </si>
+  <si>
+    <t>Saxagliptin Hcl</t>
+  </si>
+  <si>
+    <t>Onglyza, Kombiglyze</t>
+  </si>
+  <si>
+    <t>Saxagliptin Hcl/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Saxagliptin-Metformin</t>
+  </si>
+  <si>
+    <t>Sitagliptin</t>
+  </si>
+  <si>
+    <t>Sitagliptin, Zituvio</t>
+  </si>
+  <si>
+    <t>Sitagliptin Hcl</t>
+  </si>
+  <si>
+    <t>Brynovin</t>
+  </si>
+  <si>
+    <t>Sitagliptin Phosphate</t>
+  </si>
+  <si>
+    <t>Januvia</t>
+  </si>
+  <si>
+    <t>Sitagliptin Phosphate/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Janumet</t>
+  </si>
+  <si>
+    <t>Sitagliptin Phosphate/Simvastatin</t>
+  </si>
+  <si>
+    <t>Juvisync</t>
+  </si>
+  <si>
+    <t>Sitagliptin/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Sitagliptin-Metformin, Zituvimet</t>
+  </si>
+  <si>
+    <t>Zituvimet</t>
+  </si>
+  <si>
+    <t>Glimepiride</t>
+  </si>
+  <si>
+    <t>Glimepiride, Amaryl</t>
+  </si>
+  <si>
+    <t>Glipizide</t>
+  </si>
+  <si>
+    <t>Glipizide, Glucotrol</t>
+  </si>
+  <si>
+    <t>Glipizide/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Glipizide-Metformin, Metaglip</t>
+  </si>
+  <si>
+    <t>Glyburide</t>
+  </si>
+  <si>
+    <t>Diabeta, Glyburide, Micronase</t>
+  </si>
+  <si>
+    <t>Glyburide,Micronized</t>
+  </si>
+  <si>
+    <t>Glyburide Micronized, Glycron, Glynase</t>
+  </si>
+  <si>
+    <t>Glyburide/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Glucovance, Glyburide-Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Pioglitazone Hcl/Glimepiride</t>
+  </si>
+  <si>
+    <t>Duetact, Pioglitazone-Glimepiride</t>
+  </si>
+  <si>
+    <t>Pioglitazone-Glimepiride</t>
+  </si>
+  <si>
+    <t>Rosiglitazone Maleate/Glimepiride</t>
+  </si>
+  <si>
+    <t>Avandaryl</t>
+  </si>
+  <si>
+    <t>Bexagliflozin</t>
+  </si>
+  <si>
+    <t>Bexagliflozin, Brenzavvy</t>
+  </si>
+  <si>
+    <t>Canagliflozin</t>
+  </si>
+  <si>
+    <t>Invokana</t>
+  </si>
+  <si>
+    <t>Canagliflozin/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Invokamet</t>
+  </si>
+  <si>
+    <t>Dapagliflozin Propanediol</t>
+  </si>
+  <si>
+    <t>Dapagliflozin, Farxiga</t>
+  </si>
+  <si>
+    <t>Dapagliflozin Propanediol/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Dapagliflozin-Metformin, Xigduo</t>
+  </si>
+  <si>
+    <t>Empagliflozin</t>
+  </si>
+  <si>
+    <t>Jardiance</t>
+  </si>
+  <si>
+    <t>Empagliflozin/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Synjardy</t>
+  </si>
+  <si>
+    <t>Ertugliflozin Pidolate</t>
+  </si>
+  <si>
+    <t>Steglatro</t>
+  </si>
+  <si>
+    <t>Ertugliflozin Pidolate/Metformin Hcl</t>
+  </si>
+  <si>
+    <t>Segluromet</t>
+  </si>
+  <si>
+    <t>Sotagliflozin</t>
+  </si>
+  <si>
+    <t>Inpefa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -295,13 +295,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -336,10 +329,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -348,25 +341,6 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -430,6 +404,26 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -444,12 +438,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52AD553B-66EC-774F-AD1D-83DF5355B527}" name="Table2" displayName="Table2" ref="A1:C41" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52AD553B-66EC-774F-AD1D-83DF5355B527}" name="Table2" displayName="Table2" ref="A1:C41" totalsRowShown="0" headerRowDxfId="4" dataDxfId="0">
   <autoFilter ref="A1:C41" xr:uid="{52AD553B-66EC-774F-AD1D-83DF5355B527}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{16940BBC-AFB3-3343-A6A2-E5959C735CD4}" name="Group" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{59D51277-A055-3945-ADFC-602DACCAA329}" name="Generic Name" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{6C782C48-150F-A545-9CDB-54150B06CD2C}" name="Drug Names" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{16940BBC-AFB3-3343-A6A2-E5959C735CD4}" name="Group" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{59D51277-A055-3945-ADFC-602DACCAA329}" name="Generic Name" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{6C782C48-150F-A545-9CDB-54150B06CD2C}" name="Drug Names" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -777,7 +771,7 @@
   <cols>
     <col min="1" max="1" width="17.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" style="2" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
@@ -789,34 +783,38 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -825,280 +823,282 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
+    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>15</v>
+      <c r="B8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
+      <c r="B11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
+      <c r="B12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>16</v>
+      <c r="B14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>9</v>
+      <c r="B15" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
+      <c r="B16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
+    </row>
+    <row r="28" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B31" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B33" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B34" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>70</v>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B36" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B38" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>65</v>
+      <c r="B36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B38" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B39" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B40" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B41" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>67</v>
+      <c r="B41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
